--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486840_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486840_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.49</v>
+        <v>7.4587</v>
       </c>
       <c r="E2" t="n">
-        <v>9.186299999999999</v>
+        <v>7.4281</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3037</v>
+        <v>0.0306</v>
       </c>
       <c r="G2" t="n">
         <v>1.4121</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>5.279</v>
+        <v>3.2477</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9436</v>
+        <v>2.1854</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3355</v>
+        <v>1.0623</v>
       </c>
       <c r="V2" t="n">
         <v>2.4128</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8456</v>
+        <v>3.5903</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1462</v>
+        <v>4.7668</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3006</v>
+        <v>-1.1765</v>
       </c>
       <c r="G3" t="n">
         <v>5.4482</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0001</v>
+        <v>0.7446</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0832</v>
+        <v>0.5373</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.2073</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6747</v>
+        <v>3.0633</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6013</v>
+        <v>2.6355</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0735</v>
+        <v>0.4278</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1857</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3078</v>
+        <v>1.6963</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6071</v>
+        <v>0.4271</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9149</v>
+        <v>1.2692</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5712</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0943</v>
+        <v>3.0002</v>
       </c>
       <c r="E5" t="n">
-        <v>2.411</v>
+        <v>1.4756</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3167</v>
+        <v>1.5246</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0379</v>
+        <v>0.718</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1864</v>
+        <v>0.7655</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1485</v>
+        <v>-0.0475</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0458</v>
+        <v>1.5257</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.634</v>
+        <v>1.3177</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6798</v>
+        <v>0.208</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0837</v>
+        <v>-0.8077</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5524</v>
+        <v>-0.5522</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5313</v>
+        <v>-0.2555</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0609</v>
+        <v>1.3514</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1375</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1985</v>
+        <v>0.745</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2277</v>
+        <v>-0.6138</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9742</v>
+        <v>2.7273</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6483</v>
+        <v>2.7213</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3259</v>
+        <v>0.0061</v>
       </c>
       <c r="G6" t="n">
-        <v>0.718</v>
+        <v>-0.0379</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7655</v>
+        <v>-1.1864</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0475</v>
+        <v>1.1485</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5257</v>
+        <v>1.0458</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3177</v>
+        <v>-0.634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.208</v>
+        <v>1.6798</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8077</v>
+        <v>-1.0837</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5522</v>
+        <v>-0.5524</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2555</v>
+        <v>-0.5313</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3254</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.221</v>
+        <v>0.4478</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5464</v>
+        <v>0.1243</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1347</v>
+        <v>0.7443</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4169</v>
+        <v>3.0512</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2822</v>
+        <v>-2.307</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3101</v>
+        <v>1.2753</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5595</v>
+        <v>0.9588</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8696</v>
+        <v>0.3165</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6217</v>
+        <v>4.0692</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1461</v>
+        <v>2.6833</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5244</v>
+        <v>1.3858</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9318</v>
+        <v>-2.7939</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5867</v>
+        <v>-1.7246</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3451</v>
+        <v>-1.0693</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4214</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5095</v>
+        <v>0.6272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0881</v>
+        <v>0.0002</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6409</v>
+        <v>-0.0053</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9478</v>
+        <v>2.5502</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.307</v>
+        <v>-2.5555</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2753</v>
+        <v>0.4544</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9588</v>
+        <v>0.1379</v>
       </c>
       <c r="I8" t="n">
         <v>0.3165</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0692</v>
+        <v>2.0761</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6833</v>
+        <v>0.6903</v>
       </c>
       <c r="L8" t="n">
         <v>1.3858</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7939</v>
+        <v>-1.6217</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7246</v>
+        <v>-0.5524</v>
       </c>
       <c r="O8" t="n">
         <v>-1.0693</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5241</v>
+        <v>0.324</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5238</v>
+        <v>0.5168</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002</v>
+        <v>-0.1928</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5559</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>-0.0426</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2553</v>
+        <v>-0.1353</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8605</v>
+        <v>3.0724</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6051</v>
+        <v>-3.2077</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4544</v>
+        <v>-1.3101</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1379</v>
+        <v>0.5595</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3165</v>
+        <v>-1.8696</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0761</v>
+        <v>1.6217</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6903</v>
+        <v>2.1461</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3858</v>
+        <v>-0.5244</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6217</v>
+        <v>-2.9318</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5524</v>
+        <v>-1.5867</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0693</v>
+        <v>-1.3451</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5846</v>
+        <v>1.1514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.827</v>
+        <v>1.1651</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2424</v>
+        <v>-0.0136</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5559</v>
+        <v>-0.9421</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0426</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6936</v>
+        <v>-0.6439</v>
       </c>
       <c r="E10" t="n">
         <v>0.0422</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7358</v>
+        <v>-0.6861</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0202</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8053</v>
+        <v>0.855</v>
       </c>
       <c r="T10" t="n">
         <v>0.6342</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1711</v>
+        <v>0.2208</v>
       </c>
       <c r="V10" t="n">
         <v>0.3282</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CEBRIAN SOLER</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0274</v>
+        <v>-1.9999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5445</v>
+        <v>-1.2682</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4829</v>
+        <v>-0.7317</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4481</v>
+        <v>0.2828</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2071</v>
+        <v>0.0273</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2411</v>
+        <v>0.2555</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.379</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0968</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.379</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0692</v>
+        <v>-0.4697</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2071</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1379</v>
+        <v>-0.4002</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5792</v>
+        <v>-0.4758</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1655</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4137</v>
+        <v>-0.3859</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>J. CEBRIAN SOLER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6163</v>
+        <v>-2.0274</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7853</v>
+        <v>-1.5445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.831</v>
+        <v>-0.4829</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2828</v>
+        <v>-1.4481</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0273</v>
+        <v>-0.2071</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2555</v>
+        <v>-1.2411</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7524999999999999</v>
+        <v>-1.379</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0968</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6556999999999999</v>
+        <v>-1.379</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4697</v>
+        <v>-0.0692</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.2071</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4002</v>
+        <v>0.1379</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>-0.5792</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.9308</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3515</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-1.0922</v>
-      </c>
       <c r="T12" t="n">
-        <v>-0.607</v>
+        <v>-0.1655</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4852</v>
+        <v>-0.4137</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.7724</v>
+        <v>15.7723</v>
       </c>
       <c r="E13" t="n">
-        <v>24.9307</v>
+        <v>24.9306</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.158200000000001</v>
+        <v>-9.158300000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>4.588799999999999</v>
+        <v>4.5888</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6902999999999998</v>
+        <v>-0.6902999999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>5.278999999999998</v>
+        <v>5.278999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>23.6322</v>
@@ -1459,7 +1459,7 @@
         <v>-8.0031</v>
       </c>
       <c r="P13" t="n">
-        <v>2.896299999999999</v>
+        <v>2.8963</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.6194</v>
@@ -1468,13 +1468,13 @@
         <v>13.5154</v>
       </c>
       <c r="S13" t="n">
-        <v>9.5152</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>6.8918</v>
+        <v>6.8919</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6233</v>
+        <v>2.6231</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2276</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1724</v>
+        <v>5.2331</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3283</v>
+        <v>6.3975</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.156</v>
+        <v>-1.1644</v>
       </c>
       <c r="G14" t="n">
         <v>0.5656</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8497</v>
+        <v>-0.0895</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9923</v>
+        <v>0.0615</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1426</v>
+        <v>-0.151</v>
       </c>
       <c r="V14" t="n">
         <v>2.8262</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4542</v>
+        <v>1.5865</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4846</v>
+        <v>6.2778</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.0304</v>
+        <v>-4.6913</v>
       </c>
       <c r="G15" t="n">
         <v>3.3284</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7044</v>
+        <v>-1.5721</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5522</v>
+        <v>-0.759</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1522</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9421</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2387</v>
+        <v>0.4994</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.397</v>
+        <v>-0.0867</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6357</v>
+        <v>0.5861</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6206</v>
@@ -1702,13 +1702,13 @@
         <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1876</v>
+        <v>0.4482</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0552</v>
+        <v>0.2551</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2428</v>
+        <v>0.1931</v>
       </c>
       <c r="V16" t="n">
         <v>0.2856</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5214</v>
+        <v>-0.5272</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0262</v>
+        <v>2.5433</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5476</v>
+        <v>-3.0705</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4954</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.6697</v>
+        <v>-1.6755</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2417</v>
+        <v>-0.7245</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.428</v>
+        <v>-0.9509</v>
       </c>
       <c r="V17" t="n">
         <v>4.5399</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9388</v>
+        <v>-1.8064</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5444</v>
+        <v>-0.7513</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3944</v>
+        <v>-1.0552</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0894</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6217</v>
+        <v>-1.4894</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3314</v>
+        <v>-0.5383</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2903</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6142</v>
+        <v>-2.1743</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3945</v>
+        <v>-2.2911</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2198</v>
+        <v>0.1168</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5676</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.502</v>
+        <v>-0.062</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2207</v>
+        <v>-0.1173</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2813</v>
+        <v>0.0553</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5314</v>
+        <v>-2.4253</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2657</v>
+        <v>0.3549</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2658</v>
+        <v>-2.7802</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9285</v>
@@ -2014,13 +2014,13 @@
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9545</v>
+        <v>0.1516</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6347</v>
+        <v>-0.0141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3198</v>
+        <v>0.1657</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7304</v>
+        <v>-5.1678</v>
       </c>
       <c r="E21" t="n">
         <v>-1.7019</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0285</v>
+        <v>-3.4658</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9407</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6313</v>
+        <v>-2.0686</v>
       </c>
       <c r="T21" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.9691</v>
+        <v>-1.4064</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.301299999999999</v>
+        <v>-8.2324</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3774</v>
+        <v>-1.5843</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.9239</v>
+        <v>-6.6481</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8405</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4689</v>
+        <v>-0.3999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0825</v>
+        <v>-0.1244</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5513</v>
+        <v>-0.2756</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6404</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.7722</v>
+        <v>-13.0144</v>
       </c>
       <c r="E23" t="n">
         <v>9.158199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-24.9307</v>
+        <v>-22.1726</v>
       </c>
       <c r="G23" t="n">
         <v>-4.588700000000001</v>
@@ -2248,13 +2248,13 @@
         <v>10.6193</v>
       </c>
       <c r="S23" t="n">
-        <v>-9.5152</v>
+        <v>-6.7572</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.6233</v>
+        <v>-2.6232</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.891800000000001</v>
+        <v>-4.1339</v>
       </c>
       <c r="V23" t="n">
         <v>1.2277</v>
